--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064784</v>
+        <v>131064775</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442100</v>
+        <v>442085</v>
       </c>
       <c r="R2" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064775</v>
+        <v>131064773</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -803,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442085</v>
+        <v>442108</v>
       </c>
       <c r="R3" t="n">
         <v>7039138</v>
@@ -843,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064773</v>
+        <v>131064784</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442108</v>
+        <v>442100</v>
       </c>
       <c r="R4" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131064770</v>
+        <v>131064778</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442198</v>
+        <v>442145</v>
       </c>
       <c r="R9" t="n">
-        <v>7039206</v>
+        <v>7039101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1482,7 +1482,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131064778</v>
+        <v>131064770</v>
       </c>
       <c r="B10" t="n">
         <v>57884</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442145</v>
+        <v>442198</v>
       </c>
       <c r="R10" t="n">
-        <v>7039101</v>
+        <v>7039206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064781</v>
+        <v>131064780</v>
       </c>
       <c r="B18" t="n">
         <v>91805</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442200</v>
+        <v>442259</v>
       </c>
       <c r="R18" t="n">
-        <v>7039150</v>
+        <v>7039181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064780</v>
+        <v>131064781</v>
       </c>
       <c r="B19" t="n">
         <v>91805</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442259</v>
+        <v>442200</v>
       </c>
       <c r="R19" t="n">
-        <v>7039181</v>
+        <v>7039150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -2284,7 +2284,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064780</v>
+        <v>131064781</v>
       </c>
       <c r="B18" t="n">
         <v>91805</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442259</v>
+        <v>442200</v>
       </c>
       <c r="R18" t="n">
-        <v>7039181</v>
+        <v>7039150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064781</v>
+        <v>131064780</v>
       </c>
       <c r="B19" t="n">
         <v>91805</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442200</v>
+        <v>442259</v>
       </c>
       <c r="R19" t="n">
-        <v>7039150</v>
+        <v>7039181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064775</v>
+        <v>131064784</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442085</v>
+        <v>442100</v>
       </c>
       <c r="R2" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +742,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064773</v>
+        <v>131064775</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -812,7 +803,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442108</v>
+        <v>442085</v>
       </c>
       <c r="R3" t="n">
         <v>7039138</v>
@@ -852,7 +843,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064784</v>
+        <v>131064773</v>
       </c>
       <c r="B4" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442100</v>
+        <v>442108</v>
       </c>
       <c r="R4" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064772</v>
+        <v>131064781</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>91805</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442099</v>
+        <v>442200</v>
       </c>
       <c r="R17" t="n">
-        <v>7039220</v>
+        <v>7039150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,11 +2253,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,7 +2279,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064781</v>
+        <v>131064780</v>
       </c>
       <c r="B18" t="n">
         <v>91805</v>
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442200</v>
+        <v>442259</v>
       </c>
       <c r="R18" t="n">
-        <v>7039150</v>
+        <v>7039181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,10 +2376,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064780</v>
+        <v>131064772</v>
       </c>
       <c r="B19" t="n">
-        <v>91805</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442259</v>
+        <v>442099</v>
       </c>
       <c r="R19" t="n">
-        <v>7039181</v>
+        <v>7039220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,6 +2447,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064784</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131064783</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131064781</v>
       </c>
       <c r="B17" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>131064780</v>
       </c>
       <c r="B18" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B21" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,19 +2586,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2606,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R21" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,6 +2646,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2668,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,23 +2688,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R22" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,23 +2586,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2610,10 +2606,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R21" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,11 +2642,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2677,10 +2668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B22" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2679,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R22" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064784</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131064783</v>
       </c>
       <c r="B11" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131064781</v>
       </c>
       <c r="B17" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>131064780</v>
       </c>
       <c r="B18" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064784</v>
+        <v>131064775</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442100</v>
+        <v>442085</v>
       </c>
       <c r="R2" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064775</v>
+        <v>131064773</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -803,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442085</v>
+        <v>442108</v>
       </c>
       <c r="R3" t="n">
         <v>7039138</v>
@@ -843,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064773</v>
+        <v>131064784</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442108</v>
+        <v>442100</v>
       </c>
       <c r="R4" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1587,7 +1587,7 @@
         <v>131064783</v>
       </c>
       <c r="B11" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064781</v>
+        <v>131064772</v>
       </c>
       <c r="B17" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442200</v>
+        <v>442099</v>
       </c>
       <c r="R17" t="n">
-        <v>7039150</v>
+        <v>7039220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,6 +2253,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2279,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064780</v>
+        <v>131064781</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442259</v>
+        <v>442200</v>
       </c>
       <c r="R18" t="n">
-        <v>7039181</v>
+        <v>7039150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,10 +2381,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064772</v>
+        <v>131064780</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>91810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,21 +2392,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442099</v>
+        <v>442259</v>
       </c>
       <c r="R19" t="n">
-        <v>7039220</v>
+        <v>7039181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,11 +2452,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B21" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,19 +2586,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2606,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R21" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,6 +2646,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2668,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,23 +2688,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R22" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,23 +2586,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2610,10 +2606,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R21" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,11 +2642,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2677,10 +2668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2679,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R22" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064775</v>
+        <v>131064773</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442085</v>
+        <v>442108</v>
       </c>
       <c r="R2" t="n">
         <v>7039138</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064773</v>
+        <v>131064784</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,23 +788,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -812,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442108</v>
+        <v>442100</v>
       </c>
       <c r="R3" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +844,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064784</v>
+        <v>131064775</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442100</v>
+        <v>442085</v>
       </c>
       <c r="R4" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,7 +975,7 @@
         <v>131064776</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>131064768</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>131064777</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131064764</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>131064778</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>131064770</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131064783</v>
+        <v>131064766</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,19 +1595,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1615,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442292</v>
+        <v>442271</v>
       </c>
       <c r="R11" t="n">
-        <v>7039182</v>
+        <v>7039174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1655,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131064766</v>
+        <v>131064783</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,23 +1697,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442271</v>
+        <v>442292</v>
       </c>
       <c r="R12" t="n">
-        <v>7039174</v>
+        <v>7039182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131064763</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131064771</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131064769</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131064772</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064781</v>
+        <v>131064780</v>
       </c>
       <c r="B18" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442200</v>
+        <v>442259</v>
       </c>
       <c r="R18" t="n">
-        <v>7039150</v>
+        <v>7039181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064780</v>
+        <v>131064781</v>
       </c>
       <c r="B19" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442259</v>
+        <v>442200</v>
       </c>
       <c r="R19" t="n">
-        <v>7039181</v>
+        <v>7039150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,19 +2586,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2606,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R21" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,6 +2646,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2668,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,23 +2688,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R22" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2773,7 +2773,7 @@
         <v>131064774</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064773</v>
+        <v>131064775</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442108</v>
+        <v>442085</v>
       </c>
       <c r="R2" t="n">
         <v>7039138</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064784</v>
+        <v>131064773</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,19 +788,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -808,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442100</v>
+        <v>442108</v>
       </c>
       <c r="R3" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064775</v>
+        <v>131064784</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442085</v>
+        <v>442100</v>
       </c>
       <c r="R4" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,7 +975,7 @@
         <v>131064776</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>131064768</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>131064777</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131064764</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>131064778</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>131064770</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131064766</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>131064783</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131064763</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131064771</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131064769</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064772</v>
+        <v>131064781</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>91813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442099</v>
+        <v>442200</v>
       </c>
       <c r="R17" t="n">
-        <v>7039220</v>
+        <v>7039150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,11 +2253,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2282,7 @@
         <v>131064780</v>
       </c>
       <c r="B18" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,10 +2376,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064781</v>
+        <v>131064772</v>
       </c>
       <c r="B19" t="n">
-        <v>91812</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442200</v>
+        <v>442099</v>
       </c>
       <c r="R19" t="n">
-        <v>7039150</v>
+        <v>7039220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,6 +2447,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,23 +2586,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2610,10 +2606,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R21" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,11 +2642,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2677,10 +2668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B22" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2679,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R22" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2773,7 +2773,7 @@
         <v>131064774</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064775</v>
+        <v>131064784</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442085</v>
+        <v>442100</v>
       </c>
       <c r="R2" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +742,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064773</v>
+        <v>131064775</v>
       </c>
       <c r="B3" t="n">
         <v>57887</v>
@@ -812,7 +803,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442108</v>
+        <v>442085</v>
       </c>
       <c r="R3" t="n">
         <v>7039138</v>
@@ -852,7 +843,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064784</v>
+        <v>131064773</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442100</v>
+        <v>442108</v>
       </c>
       <c r="R4" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131064778</v>
+        <v>131064770</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442145</v>
+        <v>442198</v>
       </c>
       <c r="R9" t="n">
-        <v>7039101</v>
+        <v>7039206</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1482,7 +1482,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131064770</v>
+        <v>131064778</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442198</v>
+        <v>442145</v>
       </c>
       <c r="R10" t="n">
-        <v>7039206</v>
+        <v>7039101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131064766</v>
+        <v>131064783</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,23 +1595,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1619,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442271</v>
+        <v>442292</v>
       </c>
       <c r="R11" t="n">
-        <v>7039174</v>
+        <v>7039182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,11 +1651,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131064783</v>
+        <v>131064766</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,19 +1688,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1717,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442292</v>
+        <v>442271</v>
       </c>
       <c r="R12" t="n">
-        <v>7039182</v>
+        <v>7039174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,6 +1748,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -1380,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131064770</v>
+        <v>131064778</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442198</v>
+        <v>442145</v>
       </c>
       <c r="R9" t="n">
-        <v>7039206</v>
+        <v>7039101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1482,7 +1482,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131064778</v>
+        <v>131064770</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442145</v>
+        <v>442198</v>
       </c>
       <c r="R10" t="n">
-        <v>7039101</v>
+        <v>7039206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131064784</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131064775</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131064773</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131064776</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>131064768</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>131064777</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131064764</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>131064778</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>131064770</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131064783</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>131064766</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>131064779</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131064763</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131064771</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131064769</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064781</v>
+        <v>131064772</v>
       </c>
       <c r="B17" t="n">
-        <v>91813</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442200</v>
+        <v>442099</v>
       </c>
       <c r="R17" t="n">
-        <v>7039150</v>
+        <v>7039220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,6 +2253,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2287,7 @@
         <v>131064780</v>
       </c>
       <c r="B18" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,10 +2381,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064772</v>
+        <v>131064781</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>91814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,21 +2392,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442099</v>
+        <v>442200</v>
       </c>
       <c r="R19" t="n">
-        <v>7039220</v>
+        <v>7039150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,11 +2452,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
         <v>131064782</v>
       </c>
       <c r="B20" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B21" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,19 +2586,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2606,10 +2610,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R21" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,6 +2646,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2668,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,23 +2688,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R22" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2773,7 +2773,7 @@
         <v>131064774</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064784</v>
+        <v>131064775</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442100</v>
+        <v>442085</v>
       </c>
       <c r="R2" t="n">
-        <v>7039221</v>
+        <v>7039138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064775</v>
+        <v>131064773</v>
       </c>
       <c r="B3" t="n">
         <v>57888</v>
@@ -803,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442085</v>
+        <v>442108</v>
       </c>
       <c r="R3" t="n">
         <v>7039138</v>
@@ -843,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064773</v>
+        <v>131064784</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442108</v>
+        <v>442100</v>
       </c>
       <c r="R4" t="n">
-        <v>7039138</v>
+        <v>7039221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131064783</v>
+        <v>131064766</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,19 +1595,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1615,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442292</v>
+        <v>442271</v>
       </c>
       <c r="R11" t="n">
-        <v>7039182</v>
+        <v>7039174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1655,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131064766</v>
+        <v>131064783</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,23 +1697,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442271</v>
+        <v>442292</v>
       </c>
       <c r="R12" t="n">
-        <v>7039174</v>
+        <v>7039182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064772</v>
+        <v>131064780</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>91814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442099</v>
+        <v>442259</v>
       </c>
       <c r="R17" t="n">
-        <v>7039220</v>
+        <v>7039181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,11 +2253,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,7 +2279,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064780</v>
+        <v>131064781</v>
       </c>
       <c r="B18" t="n">
         <v>91814</v>
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442259</v>
+        <v>442200</v>
       </c>
       <c r="R18" t="n">
-        <v>7039181</v>
+        <v>7039150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,10 +2376,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064781</v>
+        <v>131064772</v>
       </c>
       <c r="B19" t="n">
-        <v>91814</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2392,21 +2387,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442200</v>
+        <v>442099</v>
       </c>
       <c r="R19" t="n">
-        <v>7039150</v>
+        <v>7039220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,6 +2447,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,10 +2575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131064765</v>
+        <v>131064785</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2586,23 +2586,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2610,10 +2606,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442266</v>
+        <v>442124</v>
       </c>
       <c r="R21" t="n">
-        <v>7039162</v>
+        <v>7039107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,11 +2642,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2677,10 +2668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131064785</v>
+        <v>131064765</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2679,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442124</v>
+        <v>442266</v>
       </c>
       <c r="R22" t="n">
-        <v>7039107</v>
+        <v>7039162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131064775</v>
+        <v>131064779</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442085</v>
+        <v>442245</v>
       </c>
       <c r="R2" t="n">
-        <v>7039138</v>
+        <v>7039149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131064773</v>
+        <v>131064780</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442108</v>
+        <v>442259</v>
       </c>
       <c r="R3" t="n">
-        <v>7039138</v>
+        <v>7039181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131064784</v>
+        <v>131064781</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +880,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442100</v>
+        <v>442200</v>
       </c>
       <c r="R4" t="n">
-        <v>7039221</v>
+        <v>7039150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131064776</v>
+        <v>131064782</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1007,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442082</v>
+        <v>442148</v>
       </c>
       <c r="R5" t="n">
-        <v>7039140</v>
+        <v>7039255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131064768</v>
+        <v>131064763</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442209</v>
+        <v>442230</v>
       </c>
       <c r="R6" t="n">
-        <v>7039151</v>
+        <v>7039147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,7 +1138,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131064777</v>
+        <v>131064764</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442091</v>
+        <v>442242</v>
       </c>
       <c r="R7" t="n">
-        <v>7039127</v>
+        <v>7039146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131064764</v>
+        <v>131064765</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442242</v>
+        <v>442266</v>
       </c>
       <c r="R8" t="n">
-        <v>7039146</v>
+        <v>7039162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,7 +1342,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131064778</v>
+        <v>131064766</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442145</v>
+        <v>442271</v>
       </c>
       <c r="R9" t="n">
-        <v>7039101</v>
+        <v>7039174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,7 +1444,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1482,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131064770</v>
+        <v>131064768</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442198</v>
+        <v>442209</v>
       </c>
       <c r="R10" t="n">
-        <v>7039206</v>
+        <v>7039151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131064766</v>
+        <v>131064769</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442271</v>
+        <v>442203</v>
       </c>
       <c r="R11" t="n">
-        <v>7039174</v>
+        <v>7039160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131064783</v>
+        <v>131064770</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,19 +1686,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1717,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442292</v>
+        <v>442198</v>
       </c>
       <c r="R12" t="n">
-        <v>7039182</v>
+        <v>7039206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1779,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131064779</v>
+        <v>131064771</v>
       </c>
       <c r="B13" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442245</v>
+        <v>442105</v>
       </c>
       <c r="R13" t="n">
-        <v>7039149</v>
+        <v>7039294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1876,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131064763</v>
+        <v>131064772</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442230</v>
+        <v>442099</v>
       </c>
       <c r="R14" t="n">
-        <v>7039147</v>
+        <v>7039220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131064771</v>
+        <v>131064773</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2013,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442105</v>
+        <v>442108</v>
       </c>
       <c r="R15" t="n">
-        <v>7039294</v>
+        <v>7039138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2080,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131064769</v>
+        <v>131064774</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2115,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442203</v>
+        <v>442097</v>
       </c>
       <c r="R16" t="n">
-        <v>7039160</v>
+        <v>7039147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131064780</v>
+        <v>131064775</v>
       </c>
       <c r="B17" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2217,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442259</v>
+        <v>442085</v>
       </c>
       <c r="R17" t="n">
-        <v>7039181</v>
+        <v>7039138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2279,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131064781</v>
+        <v>131064776</v>
       </c>
       <c r="B18" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2290,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2314,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442200</v>
+        <v>442082</v>
       </c>
       <c r="R18" t="n">
-        <v>7039150</v>
+        <v>7039140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,6 +2358,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2376,10 +2389,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131064772</v>
+        <v>131064777</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442099</v>
+        <v>442091</v>
       </c>
       <c r="R19" t="n">
-        <v>7039220</v>
+        <v>7039127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2464,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bohål ca 3m upp i grantickerötad granhögstubbe Även ett påbörjat på 2m</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2478,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131064782</v>
+        <v>131064778</v>
       </c>
       <c r="B20" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2489,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2513,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442148</v>
+        <v>442145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039255</v>
+        <v>7039101</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2564,11 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2572,303 +2590,6 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>131064785</v>
-      </c>
-      <c r="B21" t="n">
-        <v>91838</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Djupbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>442124</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7039107</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>131064765</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57888</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Djupbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>442266</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7039162</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>131064774</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57888</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Djupbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>442097</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7039147</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54772-2025 artfynd.xlsx
+++ b/artfynd/A 54772-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064780</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064781</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064782</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064763</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064765</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064768</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064769</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064770</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064771</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064772</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2080,6 +2150,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064773</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064775</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064776</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2488,6 +2578,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2590,8 +2685,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>